--- a/Figures Extracted + Matplotlib/Matplotlib/Master_Contains_all_Polymers_for_Matplotlib.xlsx
+++ b/Figures Extracted + Matplotlib/Matplotlib/Master_Contains_all_Polymers_for_Matplotlib.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Figures Extracted + Matplotlib\Matplotlib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95A6568-EC67-4AE4-9D17-82C5C0311294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEABD49-1234-47D7-BF02-23059078405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD067CC7-B06B-46EC-A1F2-A502DBFE1260}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="49">
   <si>
     <t>Polymer Name</t>
   </si>
@@ -90,13 +90,106 @@
   </si>
   <si>
     <t>Bi2Te3 compounds</t>
+  </si>
+  <si>
+    <t>F4TCNQ-doped P3HT</t>
+  </si>
+  <si>
+    <t>F4TCNQ-doped PBTTT-C₁₄</t>
+  </si>
+  <si>
+    <t>F4TCNQ-doped P2TDC₁₇-FT4</t>
+  </si>
+  <si>
+    <t>FTS-doped P3HT</t>
+  </si>
+  <si>
+    <t>FTS-doped PBTTT-C₁₄</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401072</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401073</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401074</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401075</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401076</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401077</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401078</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401079</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401080</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401081</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401082</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401083</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401084</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401085</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401086</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401087</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401088</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401089</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401090</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401091</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401092</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401093</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401094</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401095</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401096</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aenm.201401097</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,13 +197,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,9 +236,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,14 +576,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B15A1C-A101-442A-A179-A0F73CFBB334}">
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:D374"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -4168,7 +4284,7 @@
         <v>933.57500000000005</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>15</v>
       </c>
@@ -4179,7 +4295,7 @@
         <v>10.5290226442091</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>15</v>
       </c>
@@ -4190,7 +4306,7 @@
         <v>5.3869542049792596</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>15</v>
       </c>
@@ -4201,7 +4317,7 @@
         <v>6.0755009002286302</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>15</v>
       </c>
@@ -4212,7 +4328,7 @@
         <v>3.9538020784318801</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>15</v>
       </c>
@@ -4223,7 +4339,7 @@
         <v>3.0033914514445401</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>16</v>
       </c>
@@ -4234,7 +4350,7 @@
         <v>173.302955873364</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>16</v>
       </c>
@@ -4245,7 +4361,7 @@
         <v>17.035044938755998</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>16</v>
       </c>
@@ -4256,7 +4372,7 @@
         <v>120.80629139919699</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>17</v>
       </c>
@@ -4267,7 +4383,7 @@
         <v>212.98950732064401</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>17</v>
       </c>
@@ -4278,7 +4394,7 @@
         <v>176.30663507153901</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>17</v>
       </c>
@@ -4289,7 +4405,7 @@
         <v>159.03493558658801</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -4300,7 +4416,372 @@
         <v>143.455240506221</v>
       </c>
     </row>
+    <row r="349" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A349" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B349" s="2">
+        <v>1.4E-5</v>
+      </c>
+      <c r="C349" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D349" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A350" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B350" s="2">
+        <v>4.5000000000000003E-5</v>
+      </c>
+      <c r="C350" s="2">
+        <v>950</v>
+      </c>
+      <c r="D350" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A351" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B351" s="2">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="C351" s="2">
+        <v>550</v>
+      </c>
+      <c r="D351" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A352" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B352" s="2">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="C352" s="2">
+        <v>390</v>
+      </c>
+      <c r="D352" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A353" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B353" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="C353" s="2">
+        <v>105</v>
+      </c>
+      <c r="D353" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A354" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B354" s="2">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="C354" s="2">
+        <v>1350</v>
+      </c>
+      <c r="D354" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A355" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B355" s="2">
+        <v>9.5E-4</v>
+      </c>
+      <c r="C355" s="2">
+        <v>720</v>
+      </c>
+      <c r="D355" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A356" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B356" s="2">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="C356" s="2">
+        <v>600</v>
+      </c>
+      <c r="D356" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A357" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B357" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="C357" s="2">
+        <v>155</v>
+      </c>
+      <c r="D357" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A358" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B358" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C358" s="2">
+        <v>50</v>
+      </c>
+      <c r="D358" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A359" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B359" s="2">
+        <v>4</v>
+      </c>
+      <c r="C359" s="2">
+        <v>72</v>
+      </c>
+      <c r="D359" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A360" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B360" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="C360" s="2">
+        <v>390</v>
+      </c>
+      <c r="D360" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A361" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B361" s="2">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C361" s="2">
+        <v>370</v>
+      </c>
+      <c r="D361" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A362" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B362" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="C362" s="2">
+        <v>205</v>
+      </c>
+      <c r="D362" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A363" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B363" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="C363" s="2">
+        <v>215</v>
+      </c>
+      <c r="D363" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="A364" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B364" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C364" s="2">
+        <v>100</v>
+      </c>
+      <c r="D364" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A365" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B365" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="C365" s="2">
+        <v>750</v>
+      </c>
+      <c r="D365" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A366" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B366" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="C366" s="2">
+        <v>175</v>
+      </c>
+      <c r="D366" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A367" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B367" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C367" s="2">
+        <v>145</v>
+      </c>
+      <c r="D367" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A368" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B368" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="C368" s="2">
+        <v>110</v>
+      </c>
+      <c r="D368" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A369" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B369" s="2">
+        <v>20</v>
+      </c>
+      <c r="C369" s="2">
+        <v>75</v>
+      </c>
+      <c r="D369" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A370" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B370" s="2">
+        <v>38</v>
+      </c>
+      <c r="C370" s="2">
+        <v>65</v>
+      </c>
+      <c r="D370" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A371" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B371" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C371" s="2">
+        <v>440</v>
+      </c>
+      <c r="D371" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A372" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B372" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="C372" s="2">
+        <v>320</v>
+      </c>
+      <c r="D372" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A373" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B373" s="2">
+        <v>460</v>
+      </c>
+      <c r="C373" s="2">
+        <v>26</v>
+      </c>
+      <c r="D373" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A374" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B374" s="2">
+        <v>620</v>
+      </c>
+      <c r="C374" s="2">
+        <v>21</v>
+      </c>
+      <c r="D374" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Figures Extracted + Matplotlib/Matplotlib/Master_Contains_all_Polymers_for_Matplotlib.xlsx
+++ b/Figures Extracted + Matplotlib/Matplotlib/Master_Contains_all_Polymers_for_Matplotlib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Figures Extracted + Matplotlib\Matplotlib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEABD49-1234-47D7-BF02-23059078405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD432BAE-6EDE-48B1-8E3D-C5C7D6F2CCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD067CC7-B06B-46EC-A1F2-A502DBFE1260}"/>
   </bookViews>
@@ -239,7 +239,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -257,6 +257,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>81677</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>166071</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>241593</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>14562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A78687D0-AE54-6D95-6776-1BACC388DB39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14383831" y="1465379"/>
+          <a:ext cx="6890916" cy="4674491"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1368251</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>32196</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>83385</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>53661</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD76161D-9931-C7AE-917D-436807C8EA95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6841772" y="1309351"/>
+          <a:ext cx="7580092" cy="4765183"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4783,5 +4876,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>